--- a/spellingwordcards.xlsx
+++ b/spellingwordcards.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/atsuohabe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD89FB2D-1E07-0A43-B631-C4008F798682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_FC4146E3760C8B127B99601A2512B8A5A9115F4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vol.1" sheetId="1" r:id="rId1"/>
     <sheet name="Vol.2" sheetId="2" r:id="rId2"/>
+    <sheet name="Vol.3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="147">
   <si>
     <t>No.</t>
   </si>
@@ -32,6 +33,294 @@
     <t>Translation</t>
   </si>
   <si>
+    <t>skill</t>
+  </si>
+  <si>
+    <t>技術（ぎじゅつ）</t>
+  </si>
+  <si>
+    <t>crime</t>
+  </si>
+  <si>
+    <t>犯罪（はんざい）</t>
+  </si>
+  <si>
+    <t>grind</t>
+  </si>
+  <si>
+    <t>すりつぶす</t>
+  </si>
+  <si>
+    <t>tonight</t>
+  </si>
+  <si>
+    <t>今夜（こんや）</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>レンガ</t>
+  </si>
+  <si>
+    <t>light</t>
+  </si>
+  <si>
+    <t>光（ひかり）・軽（かる）い</t>
+  </si>
+  <si>
+    <t>live</t>
+  </si>
+  <si>
+    <t>住（す）む・生（い）きる</t>
+  </si>
+  <si>
+    <t>chill</t>
+  </si>
+  <si>
+    <t>冷（ひ）え・寒気（さむけ）</t>
+  </si>
+  <si>
+    <t>delight</t>
+  </si>
+  <si>
+    <t>大喜（おおよろこ）び</t>
+  </si>
+  <si>
+    <t>build</t>
+  </si>
+  <si>
+    <t>建（た）てる</t>
+  </si>
+  <si>
+    <t>ditch</t>
+  </si>
+  <si>
+    <t>みぞ</t>
+  </si>
+  <si>
+    <t>decide</t>
+  </si>
+  <si>
+    <t>決（き）める</t>
+  </si>
+  <si>
+    <t>witness</t>
+  </si>
+  <si>
+    <t>目撃者（もくげきしゃ）</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>風（かぜ）・巻（ま）く</t>
+  </si>
+  <si>
+    <t>district</t>
+  </si>
+  <si>
+    <t>地区（ちく）</t>
+  </si>
+  <si>
+    <t>inch</t>
+  </si>
+  <si>
+    <t>インチ</t>
+  </si>
+  <si>
+    <t>sigh</t>
+  </si>
+  <si>
+    <t>ため息</t>
+  </si>
+  <si>
+    <t>fright</t>
+  </si>
+  <si>
+    <t>恐怖（きょうふ）</t>
+  </si>
+  <si>
+    <t>remind</t>
+  </si>
+  <si>
+    <t>思（おも）い出（だ）させる</t>
+  </si>
+  <si>
+    <t>splice</t>
+  </si>
+  <si>
+    <t>つなぎ合（あ）わせる</t>
+  </si>
+  <si>
+    <t>spinning</t>
+  </si>
+  <si>
+    <t>回転（かいてん）</t>
+  </si>
+  <si>
+    <t>ticket</t>
+  </si>
+  <si>
+    <t>チケット・切符（きっぷ）</t>
+  </si>
+  <si>
+    <t>surprise</t>
+  </si>
+  <si>
+    <t>驚（おどろ）き</t>
+  </si>
+  <si>
+    <t>brighten</t>
+  </si>
+  <si>
+    <t>明（あか）るくする</t>
+  </si>
+  <si>
+    <t>blade</t>
+  </si>
+  <si>
+    <t>刃（は）</t>
+  </si>
+  <si>
+    <t>gray</t>
+  </si>
+  <si>
+    <t>灰（はい）色</t>
+  </si>
+  <si>
+    <t>past</t>
+  </si>
+  <si>
+    <t>過（か）去</t>
+  </si>
+  <si>
+    <t>quake</t>
+  </si>
+  <si>
+    <t>地（じ）しん</t>
+  </si>
+  <si>
+    <t>magic</t>
+  </si>
+  <si>
+    <t>まほう</t>
+  </si>
+  <si>
+    <t>delay</t>
+  </si>
+  <si>
+    <t>おくれ</t>
+  </si>
+  <si>
+    <t>amaze</t>
+  </si>
+  <si>
+    <t>おどろかせる</t>
+  </si>
+  <si>
+    <t>drain</t>
+  </si>
+  <si>
+    <t>水をながす</t>
+  </si>
+  <si>
+    <t>maybe</t>
+  </si>
+  <si>
+    <t>たぶん</t>
+  </si>
+  <si>
+    <t>break</t>
+  </si>
+  <si>
+    <t>こわす・休み</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>セール・売り</t>
+  </si>
+  <si>
+    <t>hang</t>
+  </si>
+  <si>
+    <t>ぶら下げる</t>
+  </si>
+  <si>
+    <t>stain</t>
+  </si>
+  <si>
+    <t>シミ・よごれ</t>
+  </si>
+  <si>
+    <t>glass</t>
+  </si>
+  <si>
+    <t>ガラス・コップ</t>
+  </si>
+  <si>
+    <t>raft</t>
+  </si>
+  <si>
+    <t>いかだ</t>
+  </si>
+  <si>
+    <t>jail</t>
+  </si>
+  <si>
+    <t>ろうや</t>
+  </si>
+  <si>
+    <t>crayon</t>
+  </si>
+  <si>
+    <t>クレヨン</t>
+  </si>
+  <si>
+    <t>fact</t>
+  </si>
+  <si>
+    <t>事実</t>
+  </si>
+  <si>
+    <t>stale</t>
+  </si>
+  <si>
+    <t>古くなった</t>
+  </si>
+  <si>
+    <t>steak</t>
+  </si>
+  <si>
+    <t>ステーキ</t>
+  </si>
+  <si>
+    <t>ashamed</t>
+  </si>
+  <si>
+    <t>はずかしい</t>
+  </si>
+  <si>
+    <t>remain</t>
+  </si>
+  <si>
+    <t>残（のこ）る</t>
+  </si>
+  <si>
+    <t>grasp</t>
+  </si>
+  <si>
+    <t>つかむ</t>
+  </si>
+  <si>
+    <t>exact</t>
+  </si>
+  <si>
+    <t>正（せい）かくな</t>
+  </si>
+  <si>
     <t>west</t>
   </si>
   <si>
@@ -77,6 +366,9 @@
     <t>steam</t>
   </si>
   <si>
+    <t>蒸（じょう）気・スチーム</t>
+  </si>
+  <si>
     <t>beast</t>
   </si>
   <si>
@@ -171,153 +463,6 @@
   </si>
   <si>
     <t>守る</t>
-  </si>
-  <si>
-    <t>blade</t>
-  </si>
-  <si>
-    <t>gray</t>
-  </si>
-  <si>
-    <t>灰（はい）色</t>
-  </si>
-  <si>
-    <t>past</t>
-  </si>
-  <si>
-    <t>過（か）去</t>
-  </si>
-  <si>
-    <t>quake</t>
-  </si>
-  <si>
-    <t>地（じ）しん</t>
-  </si>
-  <si>
-    <t>magic</t>
-  </si>
-  <si>
-    <t>まほう</t>
-  </si>
-  <si>
-    <t>delay</t>
-  </si>
-  <si>
-    <t>おくれ</t>
-  </si>
-  <si>
-    <t>amaze</t>
-  </si>
-  <si>
-    <t>おどろかせる</t>
-  </si>
-  <si>
-    <t>drain</t>
-  </si>
-  <si>
-    <t>水をながす</t>
-  </si>
-  <si>
-    <t>maybe</t>
-  </si>
-  <si>
-    <t>たぶん</t>
-  </si>
-  <si>
-    <t>break</t>
-  </si>
-  <si>
-    <t>こわす・休み</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>セール・売り</t>
-  </si>
-  <si>
-    <t>hang</t>
-  </si>
-  <si>
-    <t>ぶら下げる</t>
-  </si>
-  <si>
-    <t>stain</t>
-  </si>
-  <si>
-    <t>シミ・よごれ</t>
-  </si>
-  <si>
-    <t>glass</t>
-  </si>
-  <si>
-    <t>ガラス・コップ</t>
-  </si>
-  <si>
-    <t>raft</t>
-  </si>
-  <si>
-    <t>いかだ</t>
-  </si>
-  <si>
-    <t>jail</t>
-  </si>
-  <si>
-    <t>ろうや</t>
-  </si>
-  <si>
-    <t>crayon</t>
-  </si>
-  <si>
-    <t>クレヨン</t>
-  </si>
-  <si>
-    <t>fact</t>
-  </si>
-  <si>
-    <t>事実</t>
-  </si>
-  <si>
-    <t>stale</t>
-  </si>
-  <si>
-    <t>古くなった</t>
-  </si>
-  <si>
-    <t>steak</t>
-  </si>
-  <si>
-    <t>ステーキ</t>
-  </si>
-  <si>
-    <t>ashamed</t>
-  </si>
-  <si>
-    <t>はずかしい</t>
-  </si>
-  <si>
-    <t>remain</t>
-  </si>
-  <si>
-    <t>残（のこ）る</t>
-  </si>
-  <si>
-    <t>grasp</t>
-  </si>
-  <si>
-    <t>つかむ</t>
-  </si>
-  <si>
-    <t>exact</t>
-  </si>
-  <si>
-    <t>正（せい）かくな</t>
-  </si>
-  <si>
-    <t>刃（は）</t>
-  </si>
-  <si>
-    <t>蒸（じょう）気・スチーム</t>
   </si>
 </sst>
 </file>
@@ -716,10 +861,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -727,10 +872,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -738,10 +883,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -749,10 +894,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -760,10 +905,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -771,10 +916,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -782,10 +927,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -793,10 +938,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -804,10 +949,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -815,10 +960,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -826,10 +971,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -837,10 +982,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -848,10 +993,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -859,10 +1004,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -870,10 +1015,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -881,10 +1026,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -892,10 +1037,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -903,10 +1048,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -914,10 +1059,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -925,10 +1070,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -936,10 +1081,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -947,10 +1092,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -958,10 +1103,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -969,10 +1114,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1001,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1012,10 +1157,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1023,10 +1168,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1034,10 +1179,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1045,10 +1190,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1056,10 +1201,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1067,10 +1212,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1078,10 +1223,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1089,10 +1234,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1100,10 +1245,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1111,10 +1256,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1122,10 +1267,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1133,10 +1278,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1144,10 +1289,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1155,10 +1300,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>127</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1166,10 +1311,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1177,10 +1322,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1188,10 +1333,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>36</v>
+        <v>133</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1199,10 +1344,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>39</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1210,10 +1355,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>41</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1221,10 +1366,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1232,10 +1377,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>45</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1243,10 +1388,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1254,10 +1399,295 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>48</v>
       </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="C25" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/spellingwordcards.xlsx
+++ b/spellingwordcards.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/atsuohabe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_FC4146E3760C8B127B99601A2512B8A5A9115F4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A64930C-1E14-6B49-8075-AA648C94FCBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16080" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vol.1" sheetId="1" r:id="rId1"/>
     <sheet name="Vol.2" sheetId="2" r:id="rId2"/>
     <sheet name="Vol.3" sheetId="3" r:id="rId3"/>
+    <sheet name="Vol.4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="195">
   <si>
     <t>No.</t>
   </si>
@@ -33,6 +34,432 @@
     <t>Translation</t>
   </si>
   <si>
+    <t>block</t>
+  </si>
+  <si>
+    <t>ブロック・じゃまする</t>
+  </si>
+  <si>
+    <t>shown</t>
+  </si>
+  <si>
+    <t>見せた</t>
+  </si>
+  <si>
+    <t>oatmeal</t>
+  </si>
+  <si>
+    <t>オートミール</t>
+  </si>
+  <si>
+    <t>wrote</t>
+  </si>
+  <si>
+    <t>書いた</t>
+  </si>
+  <si>
+    <t>fellow</t>
+  </si>
+  <si>
+    <t>仲（なか）間</t>
+  </si>
+  <si>
+    <t>scold</t>
+  </si>
+  <si>
+    <t>しかる</t>
+  </si>
+  <si>
+    <t>coast</t>
+  </si>
+  <si>
+    <t>海岸</t>
+  </si>
+  <si>
+    <t>odd</t>
+  </si>
+  <si>
+    <t>変（へん）な</t>
+  </si>
+  <si>
+    <t>locate</t>
+  </si>
+  <si>
+    <t>見つける</t>
+  </si>
+  <si>
+    <t>slope</t>
+  </si>
+  <si>
+    <t>坂</t>
+  </si>
+  <si>
+    <t>throat</t>
+  </si>
+  <si>
+    <t>のど</t>
+  </si>
+  <si>
+    <t>host</t>
+  </si>
+  <si>
+    <t>online</t>
+  </si>
+  <si>
+    <t>オンライン</t>
+  </si>
+  <si>
+    <t>shock</t>
+  </si>
+  <si>
+    <t>しょうげき</t>
+  </si>
+  <si>
+    <t>solve</t>
+  </si>
+  <si>
+    <t>解（と）く</t>
+  </si>
+  <si>
+    <t>known</t>
+  </si>
+  <si>
+    <t>知られた</t>
+  </si>
+  <si>
+    <t>remote</t>
+  </si>
+  <si>
+    <t>遠い</t>
+  </si>
+  <si>
+    <t>stock</t>
+  </si>
+  <si>
+    <t>在（ざい）庫</t>
+  </si>
+  <si>
+    <t>boast</t>
+  </si>
+  <si>
+    <t>じまんする</t>
+  </si>
+  <si>
+    <t>globe</t>
+  </si>
+  <si>
+    <t>borrow</t>
+  </si>
+  <si>
+    <t>借（か）りる</t>
+  </si>
+  <si>
+    <t>compose</t>
+  </si>
+  <si>
+    <t>作曲する</t>
+  </si>
+  <si>
+    <t>rocket</t>
+  </si>
+  <si>
+    <t>ロケット</t>
+  </si>
+  <si>
+    <t>doctor</t>
+  </si>
+  <si>
+    <t>医者</t>
+  </si>
+  <si>
+    <t>blade</t>
+  </si>
+  <si>
+    <t>刃（は）</t>
+  </si>
+  <si>
+    <t>gray</t>
+  </si>
+  <si>
+    <t>灰（はい）色</t>
+  </si>
+  <si>
+    <t>past</t>
+  </si>
+  <si>
+    <t>過（か）去</t>
+  </si>
+  <si>
+    <t>quake</t>
+  </si>
+  <si>
+    <t>地（じ）しん</t>
+  </si>
+  <si>
+    <t>magic</t>
+  </si>
+  <si>
+    <t>まほう</t>
+  </si>
+  <si>
+    <t>delay</t>
+  </si>
+  <si>
+    <t>おくれ</t>
+  </si>
+  <si>
+    <t>amaze</t>
+  </si>
+  <si>
+    <t>おどろかせる</t>
+  </si>
+  <si>
+    <t>drain</t>
+  </si>
+  <si>
+    <t>水をながす</t>
+  </si>
+  <si>
+    <t>maybe</t>
+  </si>
+  <si>
+    <t>たぶん</t>
+  </si>
+  <si>
+    <t>break</t>
+  </si>
+  <si>
+    <t>こわす・休み</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>セール・売り</t>
+  </si>
+  <si>
+    <t>hang</t>
+  </si>
+  <si>
+    <t>ぶら下げる</t>
+  </si>
+  <si>
+    <t>stain</t>
+  </si>
+  <si>
+    <t>シミ・よごれ</t>
+  </si>
+  <si>
+    <t>glass</t>
+  </si>
+  <si>
+    <t>ガラス・コップ</t>
+  </si>
+  <si>
+    <t>raft</t>
+  </si>
+  <si>
+    <t>いかだ</t>
+  </si>
+  <si>
+    <t>jail</t>
+  </si>
+  <si>
+    <t>ろうや</t>
+  </si>
+  <si>
+    <t>crayon</t>
+  </si>
+  <si>
+    <t>クレヨン</t>
+  </si>
+  <si>
+    <t>fact</t>
+  </si>
+  <si>
+    <t>事実</t>
+  </si>
+  <si>
+    <t>stale</t>
+  </si>
+  <si>
+    <t>古くなった</t>
+  </si>
+  <si>
+    <t>steak</t>
+  </si>
+  <si>
+    <t>ステーキ</t>
+  </si>
+  <si>
+    <t>ashamed</t>
+  </si>
+  <si>
+    <t>はずかしい</t>
+  </si>
+  <si>
+    <t>remain</t>
+  </si>
+  <si>
+    <t>残（のこ）る</t>
+  </si>
+  <si>
+    <t>grasp</t>
+  </si>
+  <si>
+    <t>つかむ</t>
+  </si>
+  <si>
+    <t>exact</t>
+  </si>
+  <si>
+    <t>正（せい）かくな</t>
+  </si>
+  <si>
+    <t>west</t>
+  </si>
+  <si>
+    <t>西</t>
+  </si>
+  <si>
+    <t>steep</t>
+  </si>
+  <si>
+    <t>急な・けわしい</t>
+  </si>
+  <si>
+    <t>member</t>
+  </si>
+  <si>
+    <t>メンバー・会員</t>
+  </si>
+  <si>
+    <t>gleam</t>
+  </si>
+  <si>
+    <t>きらめく・かがやく</t>
+  </si>
+  <si>
+    <t>fresh</t>
+  </si>
+  <si>
+    <t>新しい・新（しん）せんな</t>
+  </si>
+  <si>
+    <t>freedom</t>
+  </si>
+  <si>
+    <t>自由</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>スピード・速さ</t>
+  </si>
+  <si>
+    <t>steam</t>
+  </si>
+  <si>
+    <t>蒸（じょう）気・スチーム</t>
+  </si>
+  <si>
+    <t>beast</t>
+  </si>
+  <si>
+    <t>けもの</t>
+  </si>
+  <si>
+    <t>believe</t>
+  </si>
+  <si>
+    <t>しんじる</t>
+  </si>
+  <si>
+    <t>speck</t>
+  </si>
+  <si>
+    <t>小さな点・しみ</t>
+  </si>
+  <si>
+    <t>kept</t>
+  </si>
+  <si>
+    <t>持っていた</t>
+  </si>
+  <si>
+    <t>cheap</t>
+  </si>
+  <si>
+    <t>安い</t>
+  </si>
+  <si>
+    <t>pretend</t>
+  </si>
+  <si>
+    <t>〜のふりをする</t>
+  </si>
+  <si>
+    <t>greed</t>
+  </si>
+  <si>
+    <t>ほしがりすぎること</t>
+  </si>
+  <si>
+    <t>shelf</t>
+  </si>
+  <si>
+    <t>たな</t>
+  </si>
+  <si>
+    <t>least</t>
+  </si>
+  <si>
+    <t>もっとも少ない</t>
+  </si>
+  <si>
+    <t>eager</t>
+  </si>
+  <si>
+    <t>ねっしんな</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>理由</t>
+  </si>
+  <si>
+    <t>chief</t>
+  </si>
+  <si>
+    <t>おもな・長</t>
+  </si>
+  <si>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>全部終わる・かんせいする</t>
+  </si>
+  <si>
+    <t>sleeve</t>
+  </si>
+  <si>
+    <t>そで</t>
+  </si>
+  <si>
+    <t>engine</t>
+  </si>
+  <si>
+    <t>エンジン</t>
+  </si>
+  <si>
+    <t>defend</t>
+  </si>
+  <si>
+    <t>守る</t>
+  </si>
+  <si>
     <t>skill</t>
   </si>
   <si>
@@ -177,292 +604,10 @@
     <t>明（あか）るくする</t>
   </si>
   <si>
-    <t>blade</t>
-  </si>
-  <si>
-    <t>刃（は）</t>
-  </si>
-  <si>
-    <t>gray</t>
-  </si>
-  <si>
-    <t>灰（はい）色</t>
-  </si>
-  <si>
-    <t>past</t>
-  </si>
-  <si>
-    <t>過（か）去</t>
-  </si>
-  <si>
-    <t>quake</t>
-  </si>
-  <si>
-    <t>地（じ）しん</t>
-  </si>
-  <si>
-    <t>magic</t>
-  </si>
-  <si>
-    <t>まほう</t>
-  </si>
-  <si>
-    <t>delay</t>
-  </si>
-  <si>
-    <t>おくれ</t>
-  </si>
-  <si>
-    <t>amaze</t>
-  </si>
-  <si>
-    <t>おどろかせる</t>
-  </si>
-  <si>
-    <t>drain</t>
-  </si>
-  <si>
-    <t>水をながす</t>
-  </si>
-  <si>
-    <t>maybe</t>
-  </si>
-  <si>
-    <t>たぶん</t>
-  </si>
-  <si>
-    <t>break</t>
-  </si>
-  <si>
-    <t>こわす・休み</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>セール・売り</t>
-  </si>
-  <si>
-    <t>hang</t>
-  </si>
-  <si>
-    <t>ぶら下げる</t>
-  </si>
-  <si>
-    <t>stain</t>
-  </si>
-  <si>
-    <t>シミ・よごれ</t>
-  </si>
-  <si>
-    <t>glass</t>
-  </si>
-  <si>
-    <t>ガラス・コップ</t>
-  </si>
-  <si>
-    <t>raft</t>
-  </si>
-  <si>
-    <t>いかだ</t>
-  </si>
-  <si>
-    <t>jail</t>
-  </si>
-  <si>
-    <t>ろうや</t>
-  </si>
-  <si>
-    <t>crayon</t>
-  </si>
-  <si>
-    <t>クレヨン</t>
-  </si>
-  <si>
-    <t>fact</t>
-  </si>
-  <si>
-    <t>事実</t>
-  </si>
-  <si>
-    <t>stale</t>
-  </si>
-  <si>
-    <t>古くなった</t>
-  </si>
-  <si>
-    <t>steak</t>
-  </si>
-  <si>
-    <t>ステーキ</t>
-  </si>
-  <si>
-    <t>ashamed</t>
-  </si>
-  <si>
-    <t>はずかしい</t>
-  </si>
-  <si>
-    <t>remain</t>
-  </si>
-  <si>
-    <t>残（のこ）る</t>
-  </si>
-  <si>
-    <t>grasp</t>
-  </si>
-  <si>
-    <t>つかむ</t>
-  </si>
-  <si>
-    <t>exact</t>
-  </si>
-  <si>
-    <t>正（せい）かくな</t>
-  </si>
-  <si>
-    <t>west</t>
-  </si>
-  <si>
-    <t>西</t>
-  </si>
-  <si>
-    <t>steep</t>
-  </si>
-  <si>
-    <t>急な・けわしい</t>
-  </si>
-  <si>
-    <t>member</t>
-  </si>
-  <si>
-    <t>メンバー・会員</t>
-  </si>
-  <si>
-    <t>gleam</t>
-  </si>
-  <si>
-    <t>きらめく・かがやく</t>
-  </si>
-  <si>
-    <t>fresh</t>
-  </si>
-  <si>
-    <t>新しい・新（しん）せんな</t>
-  </si>
-  <si>
-    <t>freedom</t>
-  </si>
-  <si>
-    <t>自由</t>
-  </si>
-  <si>
-    <t>speed</t>
-  </si>
-  <si>
-    <t>スピード・速さ</t>
-  </si>
-  <si>
-    <t>steam</t>
-  </si>
-  <si>
-    <t>蒸（じょう）気・スチーム</t>
-  </si>
-  <si>
-    <t>beast</t>
-  </si>
-  <si>
-    <t>けもの</t>
-  </si>
-  <si>
-    <t>believe</t>
-  </si>
-  <si>
-    <t>しんじる</t>
-  </si>
-  <si>
-    <t>speck</t>
-  </si>
-  <si>
-    <t>小さな点・しみ</t>
-  </si>
-  <si>
-    <t>kept</t>
-  </si>
-  <si>
-    <t>持っていた</t>
-  </si>
-  <si>
-    <t>cheap</t>
-  </si>
-  <si>
-    <t>安い</t>
-  </si>
-  <si>
-    <t>pretend</t>
-  </si>
-  <si>
-    <t>〜のふりをする</t>
-  </si>
-  <si>
-    <t>greed</t>
-  </si>
-  <si>
-    <t>ほしがりすぎること</t>
-  </si>
-  <si>
-    <t>shelf</t>
-  </si>
-  <si>
-    <t>たな</t>
-  </si>
-  <si>
-    <t>least</t>
-  </si>
-  <si>
-    <t>もっとも少ない</t>
-  </si>
-  <si>
-    <t>eager</t>
-  </si>
-  <si>
-    <t>ねっしんな</t>
-  </si>
-  <si>
-    <t>reason</t>
-  </si>
-  <si>
-    <t>理由</t>
-  </si>
-  <si>
-    <t>chief</t>
-  </si>
-  <si>
-    <t>おもな・長</t>
-  </si>
-  <si>
-    <t>complete</t>
-  </si>
-  <si>
-    <t>全部終わる・かんせいする</t>
-  </si>
-  <si>
-    <t>sleeve</t>
-  </si>
-  <si>
-    <t>そで</t>
-  </si>
-  <si>
-    <t>engine</t>
-  </si>
-  <si>
-    <t>エンジン</t>
-  </si>
-  <si>
-    <t>defend</t>
-  </si>
-  <si>
-    <t>守る</t>
+    <t>主人（しゅじん）</t>
+  </si>
+  <si>
+    <t>地球（ちきゅう）</t>
   </si>
 </sst>
 </file>
@@ -861,10 +1006,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -872,10 +1017,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -883,10 +1028,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -894,10 +1039,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -905,10 +1050,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -916,10 +1061,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -927,10 +1072,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -938,10 +1083,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -949,10 +1094,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -960,10 +1105,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -971,10 +1116,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -982,10 +1127,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -993,10 +1138,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1004,10 +1149,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1015,10 +1160,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1026,10 +1171,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1037,10 +1182,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1048,10 +1193,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1059,10 +1204,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1070,10 +1215,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1081,10 +1226,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1092,10 +1237,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1103,10 +1248,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1114,10 +1259,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1146,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1157,10 +1302,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1168,10 +1313,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1179,10 +1324,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1190,10 +1335,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1201,10 +1346,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1212,10 +1357,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1223,10 +1368,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1234,10 +1379,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1245,10 +1390,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1256,10 +1401,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1267,10 +1412,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1278,10 +1423,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1289,10 +1434,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1300,10 +1445,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1311,10 +1456,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1322,10 +1467,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1333,10 +1478,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1344,10 +1489,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1355,10 +1500,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1366,10 +1511,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1377,10 +1522,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1388,10 +1533,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1399,10 +1544,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -1431,10 +1576,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>145</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1442,10 +1587,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>147</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1453,10 +1598,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1464,10 +1609,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>151</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1475,10 +1620,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1486,10 +1631,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1497,10 +1642,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1508,10 +1653,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>159</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1519,10 +1664,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1530,10 +1675,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1541,10 +1686,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
+        <v>165</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1552,10 +1697,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>25</v>
+        <v>167</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>26</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1563,10 +1708,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>27</v>
+        <v>169</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1574,10 +1719,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>171</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>30</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1585,10 +1730,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>31</v>
+        <v>173</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>32</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1596,10 +1741,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>175</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>34</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1607,10 +1752,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>36</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1618,10 +1763,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>37</v>
+        <v>179</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>38</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1629,10 +1774,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>39</v>
+        <v>181</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>40</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1640,10 +1785,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>41</v>
+        <v>183</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>42</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1651,10 +1796,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>43</v>
+        <v>185</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>44</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1662,10 +1807,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>46</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1673,10 +1818,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>47</v>
+        <v>189</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>48</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1684,10 +1829,295 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>50</v>
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
